--- a/enterprise-identity-readiness-assessment-v1.0.xlsx
+++ b/enterprise-identity-readiness-assessment-v1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annajibgashvili/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annajibgashvili/Desktop/Chain of Though/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FCFCBB3-873D-E445-B6A8-C582AA752285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D98C0C83-98B4-DD4C-810D-1E884878D059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5440" yWindow="1560" windowWidth="16380" windowHeight="23660" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40920" yWindow="1840" windowWidth="16380" windowHeight="24940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessment" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -42,12 +39,6 @@
     <t>Enterprise Identity Readiness Assessment</t>
   </si>
   <si>
-    <t>Foundational Data Products™</t>
-  </si>
-  <si>
-    <t>© 2026 Anna Jibgashvili | www.foundationaldataproducts.com | https://foundationaldataproducts.com/tools</t>
-  </si>
-  <si>
     <t>Diagnostic Framework for Institutional Logic Articulation</t>
   </si>
   <si>
@@ -96,9 +87,6 @@
     <t>Authority boundaries for AI systems are defined architecturally, not just in policy documents</t>
   </si>
   <si>
-    <t>Institutional Logic Codification</t>
-  </si>
-  <si>
     <t>Our institutional 'way of doing things' is documented in machine-actionable formats, not just prose</t>
   </si>
   <si>
@@ -177,36 +165,18 @@
     <t>4. Subscribe to Enterprise Identity Imperative series for frameworks and case studies</t>
   </si>
   <si>
-    <t>5. Contact: anna@foundationaldataproducts.com for consultation on digitalizing institutional logic</t>
-  </si>
-  <si>
     <t>Weighted Score formula is:</t>
   </si>
   <si>
-    <t>=IF(ISBLANK(C[row]),"",C[row]*D[row]*20)</t>
-  </si>
-  <si>
     <t>What it does:</t>
   </si>
   <si>
-    <t>IF(ISBLANK(C[row]),"",...) - Checks if the Score cell is blank</t>
-  </si>
-  <si>
     <t>If blank → shows nothing</t>
   </si>
   <si>
     <t>If not blank → calculates the weighted score</t>
   </si>
   <si>
-    <t>C[row] * D[row] * 20 - The calculation:</t>
-  </si>
-  <si>
-    <t>C[row] = Score (1-5)</t>
-  </si>
-  <si>
-    <t>D[row] = Weight (varies by question)</t>
-  </si>
-  <si>
     <t>20 = Multiplier to scale to 100-point system</t>
   </si>
   <si>
@@ -241,6 +211,33 @@
   </si>
   <si>
     <t>Total score = Sum of all weighted scores</t>
+  </si>
+  <si>
+    <t>© 2026 Anna Jibgashvili | https://foundeon.com | https://foundationaldataproducts.com/tools</t>
+  </si>
+  <si>
+    <t>Institutional Logic Digitalization</t>
+  </si>
+  <si>
+    <t>=IF(ISBLANK(D[row]),"",D[row]*E[row]*20)</t>
+  </si>
+  <si>
+    <t>IF(ISBLANK(D[row]),"",...) - Checks if the Score cell is blank</t>
+  </si>
+  <si>
+    <t>D[row] * E[row] * 20 - The calculation:</t>
+  </si>
+  <si>
+    <t>D[row] = Score (1-5)</t>
+  </si>
+  <si>
+    <t>E[row] = Weight (varies by question)</t>
+  </si>
+  <si>
+    <t>5. Contact: anna@foundeon.com for consultation on digitalizing institutional logic</t>
+  </si>
+  <si>
+    <t>Foundeon</t>
   </si>
 </sst>
 </file>
@@ -256,8 +253,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -265,7 +260,6 @@
       <color rgb="FF0A2342"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -273,7 +267,6 @@
       <color rgb="FF0A2342"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <i/>
@@ -281,7 +274,6 @@
       <color rgb="FF666666"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -289,7 +281,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <i/>
@@ -297,7 +288,6 @@
       <color rgb="FF5A6C7D"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -305,7 +295,6 @@
       <color rgb="FF44546A"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -313,7 +302,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -321,49 +309,42 @@
       <color rgb="FF0A2342"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF5A6C7D"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3" tint="-0.499984740745262"/>
+      <color theme="3" tint="-0.49995422223578601"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="3" tint="-0.499984740745262"/>
+      <color theme="3" tint="-0.49995422223578601"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -371,7 +352,6 @@
       <color rgb="FF0A2342"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -379,14 +359,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF14181F"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -399,19 +377,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0A2342"/>
-        <bgColor rgb="FF10243E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F9FA"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFACD"/>
-        <bgColor rgb="FFF8F9FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -444,39 +419,11 @@
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -509,6 +456,34 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -595,7 +570,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -637,72 +612,36 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
@@ -743,7 +682,6 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -761,7 +699,6 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -785,588 +722,591 @@
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="2:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-    </row>
-    <row r="2" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="9" t="s">
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="2:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="2:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="11" t="s">
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+    </row>
+    <row r="7" spans="2:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="2:7" ht="37.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="20" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="7" t="s">
+      <c r="C8" s="20"/>
+    </row>
+    <row r="10" spans="2:7" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8" spans="2:7" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6"/>
-    </row>
-    <row r="10" spans="2:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="13" t="s">
+      <c r="D10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="E10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="F10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="G10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="13" t="s">
+    </row>
+    <row r="11" spans="2:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="C12" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-    </row>
-    <row r="12" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="4" t="s">
+      <c r="D12" s="6"/>
+      <c r="E12" s="7">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="F12" s="8" t="str">
+        <f>IF(ISBLANK(D12),"",D12*E12*20)</f>
+        <v/>
+      </c>
+      <c r="G12" s="9" t="str">
+        <f>IF(ISBLANK(D12),"",IF(D12&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="22"/>
+      <c r="C13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="D13" s="6"/>
+      <c r="E13" s="7">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="F13" s="8" t="str">
+        <f>IF(ISBLANK(D13),"",D13*E13*20)</f>
+        <v/>
+      </c>
+      <c r="G13" s="9" t="str">
+        <f>IF(ISBLANK(D13),"",IF(D13&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="22"/>
+      <c r="C14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="17">
+      <c r="D14" s="6"/>
+      <c r="E14" s="7">
+        <v>6.6600000000000006E-2</v>
+      </c>
+      <c r="F14" s="8" t="str">
+        <f>IF(ISBLANK(D14),"",D14*E14*20)</f>
+        <v/>
+      </c>
+      <c r="G14" s="9" t="str">
+        <f>IF(ISBLANK(D14),"",IF(D14&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="F12" s="18" t="str">
-        <f>IF(ISBLANK(D12),"",D12*E12*20)</f>
-        <v/>
-      </c>
-      <c r="G12" s="19"/>
-    </row>
-    <row r="13" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="4"/>
-      <c r="C13" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="17">
+      <c r="F16" s="8" t="str">
+        <f>IF(ISBLANK(D16),"",D16*E16*20)</f>
+        <v/>
+      </c>
+      <c r="G16" s="9" t="str">
+        <f>IF(ISBLANK(D16),"",IF(D16&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="22"/>
+      <c r="C17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="7">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="F13" s="18" t="str">
-        <f>IF(ISBLANK(D13),"",D13*E13*20)</f>
-        <v/>
-      </c>
-      <c r="G13" s="19" t="str">
-        <f>IF(ISBLANK(D13),"",IF(D13&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="4"/>
-      <c r="C14" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17">
+      <c r="F17" s="8" t="str">
+        <f>IF(ISBLANK(D17),"",D17*E17*20)</f>
+        <v/>
+      </c>
+      <c r="G17" s="9" t="str">
+        <f>IF(ISBLANK(D17),"",IF(D17&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="22"/>
+      <c r="C18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7">
         <v>6.6600000000000006E-2</v>
       </c>
-      <c r="F14" s="18" t="str">
-        <f>IF(ISBLANK(D14),"",D14*E14*20)</f>
-        <v/>
-      </c>
-      <c r="G14" s="19" t="str">
-        <f>IF(ISBLANK(D14),"",IF(D14&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="17">
+      <c r="F18" s="8" t="str">
+        <f>IF(ISBLANK(D18),"",D18*E18*20)</f>
+        <v/>
+      </c>
+      <c r="G18" s="9" t="str">
+        <f>IF(ISBLANK(D18),"",IF(D18&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="7">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="F16" s="18" t="str">
-        <f>IF(ISBLANK(D16),"",D16*E16*20)</f>
-        <v/>
-      </c>
-      <c r="G16" s="19" t="str">
-        <f>IF(ISBLANK(D16),"",IF(D16&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="4"/>
-      <c r="C17" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17">
+      <c r="F20" s="8" t="str">
+        <f>IF(ISBLANK(D20),"",D20*E20*20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="9" t="str">
+        <f>IF(ISBLANK(D20),"",IF(D20&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="22"/>
+      <c r="C21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="7">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="F17" s="18" t="str">
-        <f>IF(ISBLANK(D17),"",D17*E17*20)</f>
-        <v/>
-      </c>
-      <c r="G17" s="19" t="str">
-        <f>IF(ISBLANK(D17),"",IF(D17&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="4"/>
-      <c r="C18" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17">
+      <c r="F21" s="8" t="str">
+        <f>IF(ISBLANK(D21),"",D21*E21*20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="9" t="str">
+        <f>IF(ISBLANK(D21),"",IF(D21&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="22"/>
+      <c r="C22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="7">
         <v>6.6600000000000006E-2</v>
       </c>
-      <c r="F18" s="18" t="str">
-        <f>IF(ISBLANK(D18),"",D18*E18*20)</f>
-        <v/>
-      </c>
-      <c r="G18" s="19" t="str">
-        <f>IF(ISBLANK(D18),"",IF(D18&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-    </row>
-    <row r="20" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="15" t="s">
+      <c r="F22" s="8" t="str">
+        <f>IF(ISBLANK(D22),"",D22*E22*20)</f>
+        <v/>
+      </c>
+      <c r="G22" s="9" t="str">
+        <f>IF(ISBLANK(D22),"",IF(D22&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="17">
-        <v>6.6699999999999995E-2</v>
-      </c>
-      <c r="F20" s="18" t="str">
-        <f>IF(ISBLANK(D20),"",D20*E20*20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="19" t="str">
-        <f>IF(ISBLANK(D20),"",IF(D20&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="4"/>
-      <c r="C21" s="15" t="s">
+      <c r="C24" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="17">
-        <v>6.6699999999999995E-2</v>
-      </c>
-      <c r="F21" s="18" t="str">
-        <f>IF(ISBLANK(D21),"",D21*E21*20)</f>
-        <v/>
-      </c>
-      <c r="G21" s="19" t="str">
-        <f>IF(ISBLANK(D21),"",IF(D21&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="4"/>
-      <c r="C22" s="15" t="s">
+      <c r="D24" s="6"/>
+      <c r="E24" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="F24" s="8" t="str">
+        <f>IF(ISBLANK(D24),"",D24*E24*20)</f>
+        <v/>
+      </c>
+      <c r="G24" s="9" t="str">
+        <f>IF(ISBLANK(D24),"",IF(D24&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="22"/>
+      <c r="C25" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="17">
-        <v>6.6600000000000006E-2</v>
-      </c>
-      <c r="F22" s="18" t="str">
-        <f>IF(ISBLANK(D22),"",D22*E22*20)</f>
-        <v/>
-      </c>
-      <c r="G22" s="19" t="str">
-        <f>IF(ISBLANK(D22),"",IF(D22&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-    </row>
-    <row r="24" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="4" t="s">
+      <c r="D25" s="6"/>
+      <c r="E25" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="F25" s="8" t="str">
+        <f>IF(ISBLANK(D25),"",D25*E25*20)</f>
+        <v/>
+      </c>
+      <c r="G25" s="9" t="str">
+        <f>IF(ISBLANK(D25),"",IF(D25&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="22"/>
+      <c r="C26" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="D26" s="6"/>
+      <c r="E26" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="F26" s="8" t="str">
+        <f>IF(ISBLANK(D26),"",D26*E26*20)</f>
+        <v/>
+      </c>
+      <c r="G26" s="9" t="str">
+        <f>IF(ISBLANK(D26),"",IF(D26&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="17">
+      <c r="C28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="6"/>
+      <c r="E28" s="7">
         <v>0.05</v>
       </c>
-      <c r="F24" s="18" t="str">
-        <f>IF(ISBLANK(D24),"",D24*E24*20)</f>
-        <v/>
-      </c>
-      <c r="G24" s="19" t="str">
-        <f>IF(ISBLANK(D24),"",IF(D24&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="4"/>
-      <c r="C25" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="17">
+      <c r="F28" s="8" t="str">
+        <f>IF(ISBLANK(D28),"",D28*E28*20)</f>
+        <v/>
+      </c>
+      <c r="G28" s="9" t="str">
+        <f>IF(ISBLANK(D28),"",IF(D28&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="22"/>
+      <c r="C29" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="7">
         <v>0.05</v>
       </c>
-      <c r="F25" s="18" t="str">
-        <f>IF(ISBLANK(D25),"",D25*E25*20)</f>
-        <v/>
-      </c>
-      <c r="G25" s="19" t="str">
-        <f>IF(ISBLANK(D25),"",IF(D25&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="4"/>
-      <c r="C26" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="17">
+      <c r="F29" s="8" t="str">
+        <f>IF(ISBLANK(D29),"",D29*E29*20)</f>
+        <v/>
+      </c>
+      <c r="G29" s="9" t="str">
+        <f>IF(ISBLANK(D29),"",IF(D29&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="22"/>
+      <c r="C30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="7">
         <v>0.05</v>
       </c>
-      <c r="F26" s="18" t="str">
-        <f>IF(ISBLANK(D26),"",D26*E26*20)</f>
-        <v/>
-      </c>
-      <c r="G26" s="19" t="str">
-        <f>IF(ISBLANK(D26),"",IF(D26&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-    </row>
-    <row r="28" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="15" t="s">
+      <c r="F30" s="8" t="str">
+        <f>IF(ISBLANK(D30),"",D30*E30*20)</f>
+        <v/>
+      </c>
+      <c r="G30" s="9" t="str">
+        <f>IF(ISBLANK(D30),"",IF(D30&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="17">
-        <v>0.05</v>
-      </c>
-      <c r="F28" s="18" t="str">
-        <f>IF(ISBLANK(D28),"",D28*E28*20)</f>
-        <v/>
-      </c>
-      <c r="G28" s="19" t="str">
-        <f>IF(ISBLANK(D28),"",IF(D28&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="4"/>
-      <c r="C29" s="15" t="s">
+      <c r="C32" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="17">
-        <v>0.05</v>
-      </c>
-      <c r="F29" s="18" t="str">
-        <f>IF(ISBLANK(D29),"",D29*E29*20)</f>
-        <v/>
-      </c>
-      <c r="G29" s="19" t="str">
-        <f>IF(ISBLANK(D29),"",IF(D29&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="4"/>
-      <c r="C30" s="15" t="s">
+      <c r="D32" s="6"/>
+      <c r="E32" s="7">
+        <v>3.3399999999999999E-2</v>
+      </c>
+      <c r="F32" s="8" t="str">
+        <f>IF(ISBLANK(D32),"",D32*E32*20)</f>
+        <v/>
+      </c>
+      <c r="G32" s="9" t="str">
+        <f>IF(ISBLANK(D32),"",IF(D32&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="22"/>
+      <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="17">
-        <v>0.05</v>
-      </c>
-      <c r="F30" s="18" t="str">
-        <f>IF(ISBLANK(D30),"",D30*E30*20)</f>
-        <v/>
-      </c>
-      <c r="G30" s="19" t="str">
-        <f>IF(ISBLANK(D30),"",IF(D30&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-    </row>
-    <row r="32" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="4" t="s">
+      <c r="D33" s="6"/>
+      <c r="E33" s="7">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="F33" s="8" t="str">
+        <f>IF(ISBLANK(D33),"",D33*E33*20)</f>
+        <v/>
+      </c>
+      <c r="G33" s="9" t="str">
+        <f>IF(ISBLANK(D33),"",IF(D33&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="22"/>
+      <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="D34" s="6"/>
+      <c r="E34" s="7">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="F34" s="8" t="str">
+        <f>IF(ISBLANK(D34),"",D34*E34*20)</f>
+        <v/>
+      </c>
+      <c r="G34" s="9" t="str">
+        <f>IF(ISBLANK(D34),"",IF(D34&gt;=4,"Strong","Needs Work"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="2:7" s="10" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="17">
-        <v>3.3399999999999999E-2</v>
-      </c>
-      <c r="F32" s="18" t="str">
-        <f>IF(ISBLANK(D32),"",D32*E32*20)</f>
-        <v/>
-      </c>
-      <c r="G32" s="19" t="str">
-        <f>IF(ISBLANK(D32),"",IF(D32&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="4"/>
-      <c r="C33" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="17">
-        <v>3.3300000000000003E-2</v>
-      </c>
-      <c r="F33" s="18" t="str">
-        <f>IF(ISBLANK(D33),"",D33*E33*20)</f>
-        <v/>
-      </c>
-      <c r="G33" s="19" t="str">
-        <f>IF(ISBLANK(D33),"",IF(D33&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="4"/>
-      <c r="C34" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="17">
-        <v>3.3300000000000003E-2</v>
-      </c>
-      <c r="F34" s="18" t="str">
-        <f>IF(ISBLANK(D34),"",D34*E34*20)</f>
-        <v/>
-      </c>
-      <c r="G34" s="19" t="str">
-        <f>IF(ISBLANK(D34),"",IF(D34&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="2:7" s="20" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="23">
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="13">
         <f>SUM(F11:F35)</f>
         <v>0</v>
       </c>
-      <c r="G36" s="22"/>
-    </row>
-    <row r="38" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="3" t="s">
+      <c r="G36" s="12"/>
+    </row>
+    <row r="38" spans="2:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+    </row>
+    <row r="39" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+    </row>
+    <row r="40" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+    </row>
+    <row r="41" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-    </row>
-    <row r="39" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="2" t="s">
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+    </row>
+    <row r="42" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="2" t="s">
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+    </row>
+    <row r="44" spans="2:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="2" t="s">
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
+    </row>
+    <row r="45" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="2" t="s">
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
+    </row>
+    <row r="46" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="44" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="1" t="s">
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+    </row>
+    <row r="47" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-    </row>
-    <row r="45" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="2" t="s">
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+    </row>
+    <row r="48" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+    </row>
+    <row r="49" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -1399,8 +1339,7 @@
     <mergeCell ref="B6:G6"/>
     <mergeCell ref="B8:C8"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1413,112 +1352,111 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B2" s="24" t="s">
-        <v>47</v>
+      <c r="B2" s="14" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B4" s="25" t="s">
-        <v>48</v>
+      <c r="B4" s="15" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B6" s="24" t="s">
-        <v>49</v>
+      <c r="B6" s="14" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B8" s="24" t="s">
-        <v>50</v>
+      <c r="B8" s="14" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B11" s="24" t="s">
-        <v>53</v>
+      <c r="B11" s="14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B12" s="24" t="s">
-        <v>54</v>
+      <c r="B12" s="14" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B13" s="24" t="s">
-        <v>55</v>
+      <c r="B13" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B14" s="24" t="s">
-        <v>56</v>
+      <c r="B14" s="14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B16" s="24" t="s">
-        <v>57</v>
+      <c r="B16" s="14" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B22" s="24" t="s">
-        <v>61</v>
+      <c r="B22" s="14" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B28" s="24" t="s">
-        <v>65</v>
+      <c r="B28" s="14" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/enterprise-identity-readiness-assessment-v1.0.xlsx
+++ b/enterprise-identity-readiness-assessment-v1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annajibgashvili/Desktop/Chain of Though/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annajibgashvili/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D98C0C83-98B4-DD4C-810D-1E884878D059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2586AC5B-09D7-FB40-BB41-4EDA12126F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40920" yWindow="1840" windowWidth="16380" windowHeight="24940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="42940" windowHeight="28200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessment" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -39,6 +42,12 @@
     <t>Enterprise Identity Readiness Assessment</t>
   </si>
   <si>
+    <t>Foundeon</t>
+  </si>
+  <si>
+    <t>© 2026 Anna Jibgashvili  |  www.foundeon.com  |  https://foundeon.com/eira</t>
+  </si>
+  <si>
     <t>Diagnostic Framework for Institutional Logic Articulation</t>
   </si>
   <si>
@@ -87,6 +96,9 @@
     <t>Authority boundaries for AI systems are defined architecturally, not just in policy documents</t>
   </si>
   <si>
+    <t>Institutional Logic Digitalization</t>
+  </si>
+  <si>
     <t>Our institutional 'way of doing things' is documented in machine-actionable formats, not just prose</t>
   </si>
   <si>
@@ -138,45 +150,63 @@
     <t>SCORE INTERPRETATION</t>
   </si>
   <si>
-    <t>80-100: READY: Strong institutional identity foundation. Focus on maintaining clarity as AI scales.</t>
-  </si>
-  <si>
-    <t>60-79: PROGRESSING: Key elements in place, but critical gaps remain. Prioritize trade-off articulation and decision boundaries.</t>
-  </si>
-  <si>
-    <t>40-59: AT RISK: Significant structural ambiguity. AI delegation without articulation will likely result in convergence.</t>
-  </si>
-  <si>
-    <t>0-39: URGENT: Institutional logic largely tacit. Immediate action required before AI systems harden around defaults.</t>
+    <t>80-100  READY:  Your institutional logic is articulated clearly enough for AI to operate on it. The work now is holding that clarity as AI scales across more workflows and decisions. Board-ready line: "We have established that our institutional logic is explicit and owned, and we are positioned to scale AI on foundations we control."</t>
+  </si>
+  <si>
+    <t>60-79  PROGRESSING:  The core of your institutional identity is in place, with specific dimensions ready to be made more explicit. Trade-Off Articulation and Decision Boundaries are the highest-leverage dimensions to formalize next. Board-ready line: "Our foundations are largely in place. We have identified the specific dimensions to formalize before we scale AI further, and we have a path to close them."</t>
+  </si>
+  <si>
+    <t>40-59  EMERGING:  Several dimensions of your institutional logic are ready to be moved from tacit understanding into explicit, machine-readable form. Articulating these before delegating decisions to AI keeps your operating logic distinct and owned as you scale. Board-ready line: "We have a clear read on which foundations to establish before we delegate decisions to AI, and we are sequencing that work deliberately."</t>
+  </si>
+  <si>
+    <t>0-39  FOUNDATIONAL:  This is the moment to author your institutional logic explicitly, before AI systems operate on defaults in its place. Making meaning, decision rights, and governance explicit now keeps them enterprise-owned as AI enters your workflows. Board-ready line: "We are establishing the foundations our AI program will run on now, so that our institutional logic remains explicit, owned, and governed as we scale."</t>
   </si>
   <si>
     <t>NEXT STEPS</t>
   </si>
   <si>
-    <t>1. Review dimensions scoring below 4 - these represent structural gaps that AI will inherit</t>
-  </si>
-  <si>
-    <t>2. Prioritize 'Trade-Off Articulation' and 'Decision Boundaries' - foundational for delegation</t>
-  </si>
-  <si>
-    <t>3. Share results with leadership to align on institutional identity work</t>
-  </si>
-  <si>
-    <t>4. Subscribe to Enterprise Identity Imperative series for frameworks and case studies</t>
+    <t>1. Review any dimension scoring below 4. These are the foundations to make explicit before AI operates on them at scale.</t>
+  </si>
+  <si>
+    <t>2. Start with Trade-Off Articulation and Decision Boundaries. These two dimensions are foundational to everything you delegate to AI.</t>
+  </si>
+  <si>
+    <t>3. Share this read with leadership. It gives you a defensible, board-ready statement of where the enterprise stands and what comes next.</t>
+  </si>
+  <si>
+    <t>4. Turn the read into a build order. The Workflow Disposition Engagement reads each of your AI-candidate workflows against the readiness this assessment measures, assigns each a disposition, and returns a sequenced build order you can commit capital to. Scope and outcomes depend on the selected engagement model.</t>
+  </si>
+  <si>
+    <t>5. Scope it in one executive conversation. Contact anna@foundeon.com to map your workflow population and confirm the path.</t>
   </si>
   <si>
     <t>Weighted Score formula is:</t>
   </si>
   <si>
+    <t>=IF(ISBLANK(C[row]),"",C[row]*D[row]*20)</t>
+  </si>
+  <si>
     <t>What it does:</t>
   </si>
   <si>
+    <t>IF(ISBLANK(C[row]),"",...) - Checks if the Score cell is blank</t>
+  </si>
+  <si>
     <t>If blank → shows nothing</t>
   </si>
   <si>
     <t>If not blank → calculates the weighted score</t>
   </si>
   <si>
+    <t>C[row] * D[row] * 20 - The calculation:</t>
+  </si>
+  <si>
+    <t>C[row] = Score (1-5)</t>
+  </si>
+  <si>
+    <t>D[row] = Weight (varies by question)</t>
+  </si>
+  <si>
     <t>20 = Multiplier to scale to 100-point system</t>
   </si>
   <si>
@@ -211,48 +241,27 @@
   </si>
   <si>
     <t>Total score = Sum of all weighted scores</t>
-  </si>
-  <si>
-    <t>© 2026 Anna Jibgashvili | https://foundeon.com | https://foundationaldataproducts.com/tools</t>
-  </si>
-  <si>
-    <t>Institutional Logic Digitalization</t>
-  </si>
-  <si>
-    <t>=IF(ISBLANK(D[row]),"",D[row]*E[row]*20)</t>
-  </si>
-  <si>
-    <t>IF(ISBLANK(D[row]),"",...) - Checks if the Score cell is blank</t>
-  </si>
-  <si>
-    <t>D[row] * E[row] * 20 - The calculation:</t>
-  </si>
-  <si>
-    <t>D[row] = Score (1-5)</t>
-  </si>
-  <si>
-    <t>E[row] = Weight (varies by question)</t>
-  </si>
-  <si>
-    <t>5. Contact: anna@foundeon.com for consultation on digitalizing institutional logic</t>
-  </si>
-  <si>
-    <t>Foundeon</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
+  <numFmts count="1">
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -260,6 +269,7 @@
       <color rgb="FF0A2342"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -267,6 +277,7 @@
       <color rgb="FF0A2342"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i/>
@@ -274,6 +285,7 @@
       <color rgb="FF666666"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -281,6 +293,7 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i/>
@@ -288,6 +301,7 @@
       <color rgb="FF5A6C7D"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -295,6 +309,7 @@
       <color rgb="FF44546A"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -302,6 +317,7 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -309,42 +325,49 @@
       <color rgb="FF0A2342"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF5A6C7D"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3" tint="-0.49995422223578601"/>
+      <color theme="3" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="3" tint="-0.49995422223578601"/>
+      <color theme="3" tint="-0.499984740745262"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -352,6 +375,7 @@
       <color rgb="FF0A2342"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -359,12 +383,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF14181F"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -377,16 +403,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0A2342"/>
+        <bgColor rgb="FF10243E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F9FA"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFACD"/>
+        <bgColor rgb="FFF8F9FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -414,79 +443,82 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -570,7 +602,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -612,36 +644,72 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
@@ -682,6 +750,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -699,6 +768,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -722,591 +792,588 @@
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="16" t="s">
+    <row r="1" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-    </row>
-    <row r="2" spans="2:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="18" t="s">
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-    </row>
-    <row r="6" spans="2:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-    </row>
-    <row r="7" spans="2:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="2:7" ht="37.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="20"/>
-    </row>
-    <row r="10" spans="2:7" ht="38" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="3" t="s">
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+    </row>
+    <row r="6" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+    </row>
+    <row r="8" spans="2:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="C8" s="6"/>
+    </row>
+    <row r="10" spans="2:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="C10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="D10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="E10" s="13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="2:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="22" t="s">
+      <c r="F10" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="G10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7">
+    </row>
+    <row r="11" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="25">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="F12" s="8" t="str">
+      <c r="F12" s="17" t="str">
         <f>IF(ISBLANK(D12),"",D12*E12*20)</f>
         <v/>
       </c>
-      <c r="G12" s="9" t="str">
-        <f>IF(ISBLANK(D12),"",IF(D12&gt;=4,"Strong","Needs Work"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="22"/>
-      <c r="C13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7">
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="4"/>
+      <c r="C13" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="16"/>
+      <c r="E13" s="25">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="F13" s="8" t="str">
+      <c r="F13" s="17" t="str">
         <f>IF(ISBLANK(D13),"",D13*E13*20)</f>
         <v/>
       </c>
-      <c r="G13" s="9" t="str">
+      <c r="G13" s="18" t="str">
         <f>IF(ISBLANK(D13),"",IF(D13&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="22"/>
-      <c r="C14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="7">
+    <row r="14" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="4"/>
+      <c r="C14" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="25">
         <v>6.6600000000000006E-2</v>
       </c>
-      <c r="F14" s="8" t="str">
+      <c r="F14" s="17" t="str">
         <f>IF(ISBLANK(D14),"",D14*E14*20)</f>
         <v/>
       </c>
-      <c r="G14" s="9" t="str">
+      <c r="G14" s="18" t="str">
         <f>IF(ISBLANK(D14),"",IF(D14&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7">
+    <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="16"/>
+      <c r="E16" s="25">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="F16" s="8" t="str">
+      <c r="F16" s="17" t="str">
         <f>IF(ISBLANK(D16),"",D16*E16*20)</f>
         <v/>
       </c>
-      <c r="G16" s="9" t="str">
+      <c r="G16" s="18" t="str">
         <f>IF(ISBLANK(D16),"",IF(D16&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="22"/>
-      <c r="C17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7">
+    <row r="17" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="4"/>
+      <c r="C17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="16"/>
+      <c r="E17" s="25">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="F17" s="8" t="str">
+      <c r="F17" s="17" t="str">
         <f>IF(ISBLANK(D17),"",D17*E17*20)</f>
         <v/>
       </c>
-      <c r="G17" s="9" t="str">
+      <c r="G17" s="18" t="str">
         <f>IF(ISBLANK(D17),"",IF(D17&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="22"/>
-      <c r="C18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7">
+    <row r="18" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="4"/>
+      <c r="C18" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="16"/>
+      <c r="E18" s="25">
         <v>6.6600000000000006E-2</v>
       </c>
-      <c r="F18" s="8" t="str">
+      <c r="F18" s="17" t="str">
         <f>IF(ISBLANK(D18),"",D18*E18*20)</f>
         <v/>
       </c>
-      <c r="G18" s="9" t="str">
+      <c r="G18" s="18" t="str">
         <f>IF(ISBLANK(D18),"",IF(D18&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="7">
+    <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="16"/>
+      <c r="E20" s="25">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="F20" s="8" t="str">
+      <c r="F20" s="17" t="str">
         <f>IF(ISBLANK(D20),"",D20*E20*20)</f>
         <v/>
       </c>
-      <c r="G20" s="9" t="str">
+      <c r="G20" s="18" t="str">
         <f>IF(ISBLANK(D20),"",IF(D20&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="22"/>
-      <c r="C21" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="7">
+    <row r="21" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="4"/>
+      <c r="C21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="16"/>
+      <c r="E21" s="25">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="F21" s="8" t="str">
+      <c r="F21" s="17" t="str">
         <f>IF(ISBLANK(D21),"",D21*E21*20)</f>
         <v/>
       </c>
-      <c r="G21" s="9" t="str">
+      <c r="G21" s="18" t="str">
         <f>IF(ISBLANK(D21),"",IF(D21&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="22"/>
-      <c r="C22" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="7">
+    <row r="22" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="4"/>
+      <c r="C22" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="E22" s="25">
         <v>6.6600000000000006E-2</v>
       </c>
-      <c r="F22" s="8" t="str">
+      <c r="F22" s="17" t="str">
         <f>IF(ISBLANK(D22),"",D22*E22*20)</f>
         <v/>
       </c>
-      <c r="G22" s="9" t="str">
+      <c r="G22" s="18" t="str">
         <f>IF(ISBLANK(D22),"",IF(D22&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="7">
+    <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+    </row>
+    <row r="24" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="16"/>
+      <c r="E24" s="25">
         <v>0.05</v>
       </c>
-      <c r="F24" s="8" t="str">
+      <c r="F24" s="17" t="str">
         <f>IF(ISBLANK(D24),"",D24*E24*20)</f>
         <v/>
       </c>
-      <c r="G24" s="9" t="str">
+      <c r="G24" s="18" t="str">
         <f>IF(ISBLANK(D24),"",IF(D24&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="22"/>
-      <c r="C25" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="7">
+    <row r="25" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="4"/>
+      <c r="C25" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="16"/>
+      <c r="E25" s="25">
         <v>0.05</v>
       </c>
-      <c r="F25" s="8" t="str">
+      <c r="F25" s="17" t="str">
         <f>IF(ISBLANK(D25),"",D25*E25*20)</f>
         <v/>
       </c>
-      <c r="G25" s="9" t="str">
+      <c r="G25" s="18" t="str">
         <f>IF(ISBLANK(D25),"",IF(D25&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="22"/>
-      <c r="C26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="7">
+    <row r="26" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="4"/>
+      <c r="C26" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="16"/>
+      <c r="E26" s="25">
         <v>0.05</v>
       </c>
-      <c r="F26" s="8" t="str">
+      <c r="F26" s="17" t="str">
         <f>IF(ISBLANK(D26),"",D26*E26*20)</f>
         <v/>
       </c>
-      <c r="G26" s="9" t="str">
+      <c r="G26" s="18" t="str">
         <f>IF(ISBLANK(D26),"",IF(D26&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-    </row>
-    <row r="28" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="7">
+    <row r="27" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+    </row>
+    <row r="28" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="16"/>
+      <c r="E28" s="25">
         <v>0.05</v>
       </c>
-      <c r="F28" s="8" t="str">
+      <c r="F28" s="17" t="str">
         <f>IF(ISBLANK(D28),"",D28*E28*20)</f>
         <v/>
       </c>
-      <c r="G28" s="9" t="str">
+      <c r="G28" s="18" t="str">
         <f>IF(ISBLANK(D28),"",IF(D28&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="22"/>
-      <c r="C29" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="7">
+    <row r="29" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="4"/>
+      <c r="C29" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="16"/>
+      <c r="E29" s="25">
         <v>0.05</v>
       </c>
-      <c r="F29" s="8" t="str">
+      <c r="F29" s="17" t="str">
         <f>IF(ISBLANK(D29),"",D29*E29*20)</f>
         <v/>
       </c>
-      <c r="G29" s="9" t="str">
+      <c r="G29" s="18" t="str">
         <f>IF(ISBLANK(D29),"",IF(D29&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="22"/>
-      <c r="C30" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="7">
+    <row r="30" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="4"/>
+      <c r="C30" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="16"/>
+      <c r="E30" s="25">
         <v>0.05</v>
       </c>
-      <c r="F30" s="8" t="str">
+      <c r="F30" s="17" t="str">
         <f>IF(ISBLANK(D30),"",D30*E30*20)</f>
         <v/>
       </c>
-      <c r="G30" s="9" t="str">
+      <c r="G30" s="18" t="str">
         <f>IF(ISBLANK(D30),"",IF(D30&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-    </row>
-    <row r="32" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D32" s="6"/>
-      <c r="E32" s="7">
+    <row r="31" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="16"/>
+      <c r="E32" s="25">
         <v>3.3399999999999999E-2</v>
       </c>
-      <c r="F32" s="8" t="str">
+      <c r="F32" s="17" t="str">
         <f>IF(ISBLANK(D32),"",D32*E32*20)</f>
         <v/>
       </c>
-      <c r="G32" s="9" t="str">
+      <c r="G32" s="18" t="str">
         <f>IF(ISBLANK(D32),"",IF(D32&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="22"/>
-      <c r="C33" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="7">
+    <row r="33" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="4"/>
+      <c r="C33" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="16"/>
+      <c r="E33" s="25">
         <v>3.3300000000000003E-2</v>
       </c>
-      <c r="F33" s="8" t="str">
+      <c r="F33" s="17" t="str">
         <f>IF(ISBLANK(D33),"",D33*E33*20)</f>
         <v/>
       </c>
-      <c r="G33" s="9" t="str">
+      <c r="G33" s="18" t="str">
         <f>IF(ISBLANK(D33),"",IF(D33&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="22"/>
-      <c r="C34" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="7">
+    <row r="34" spans="2:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="4"/>
+      <c r="C34" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="16"/>
+      <c r="E34" s="25">
         <v>3.3300000000000003E-2</v>
       </c>
-      <c r="F34" s="8" t="str">
+      <c r="F34" s="17" t="str">
         <f>IF(ISBLANK(D34),"",D34*E34*20)</f>
         <v/>
       </c>
-      <c r="G34" s="9" t="str">
+      <c r="G34" s="18" t="str">
         <f>IF(ISBLANK(D34),"",IF(D34&gt;=4,"Strong","Needs Work"))</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="2:7" s="10" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="13">
+    <row r="36" spans="2:7" s="19" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="22">
         <f>SUM(F11:F35)</f>
         <v>0</v>
       </c>
-      <c r="G36" s="12"/>
-    </row>
-    <row r="38" spans="2:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-    </row>
-    <row r="39" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-    </row>
-    <row r="40" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-    </row>
-    <row r="41" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="24" t="s">
+      <c r="G36" s="21"/>
+    </row>
+    <row r="38" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-    </row>
-    <row r="42" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="24" t="s">
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+    </row>
+    <row r="39" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-    </row>
-    <row r="44" spans="2:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="25" t="s">
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-    </row>
-    <row r="45" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="24" t="s">
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
-    </row>
-    <row r="46" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="24" t="s">
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-    </row>
-    <row r="47" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="24" t="s">
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="44" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-    </row>
-    <row r="48" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="24" t="s">
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-    </row>
-    <row r="49" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+    </row>
+    <row r="46" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -1339,7 +1406,8 @@
     <mergeCell ref="B6:G6"/>
     <mergeCell ref="B8:C8"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -1351,112 +1419,113 @@
     <col min="2" max="2" width="45.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B2" s="14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B4" s="15" t="s">
+    <row r="2" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B6" s="14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B8" s="14" t="s">
+    <row r="24" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B11" s="14" t="s">
+    <row r="25" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B12" s="14" t="s">
+    <row r="26" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B13" s="14" t="s">
+    <row r="28" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="23" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B14" s="14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B16" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B22" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B28" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>